--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.4480,0.0273,0.4649,0.1566</t>
-  </si>
-  <si>
-    <t>0.0293,0.0043,0.0025,0.9837</t>
-  </si>
-  <si>
-    <t>0.7360,0.0438,0.0508,0.2263</t>
-  </si>
-  <si>
-    <t>0.0204,0.0556,0.0160,0.9786</t>
-  </si>
-  <si>
-    <t>0.9965,0.0009,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0017,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9951,0.0011,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9930,0.0023,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.5923,0.0462,0.4177,0.0028</t>
-  </si>
-  <si>
-    <t>0.2725,0.0136,0.8120,0.0046</t>
-  </si>
-  <si>
-    <t>0.7183,0.0161,0.4242,0.0011</t>
-  </si>
-  <si>
-    <t>0.0264,0.0089,0.9661,0.0015</t>
-  </si>
-  <si>
-    <t>0.6572,0.1563,0.2471,0.0253</t>
-  </si>
-  <si>
-    <t>0.0196,0.9735,0.0041,0.0022</t>
-  </si>
-  <si>
-    <t>0.0128,0.9813,0.0025,0.0016</t>
-  </si>
-  <si>
-    <t>0.3193,0.7564,0.0040,0.0074</t>
-  </si>
-  <si>
-    <t>0.0218,0.9670,0.0046,0.0022</t>
-  </si>
-  <si>
-    <t>0.0016,0.9955,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.2092,0.0096,0.7699,0.0394</t>
-  </si>
-  <si>
-    <t>0.3745,0.0332,0.6775,0.0065</t>
-  </si>
-  <si>
-    <t>0.0174,0.0034,0.9750,0.0032</t>
-  </si>
-  <si>
-    <t>0.1450,0.0037,0.8703,0.0146</t>
-  </si>
-  <si>
-    <t>0.2030,0.0026,0.8878,0.0016</t>
-  </si>
-  <si>
-    <t>0.0960,0.0307,0.8830,0.0071</t>
-  </si>
-  <si>
-    <t>0.0017,0.0010,0.9949,0.0025</t>
-  </si>
-  <si>
-    <t>0.6439,0.4497,0.0158,0.0053</t>
-  </si>
-  <si>
-    <t>0.8636,0.0762,0.0796,0.0052</t>
-  </si>
-  <si>
-    <t>0.0079,0.0267,0.9765,0.0152</t>
-  </si>
-  <si>
-    <t>0.1027,0.7710,0.1415,0.0019</t>
-  </si>
-  <si>
-    <t>0.9227,0.0430,0.0202,0.0071</t>
-  </si>
-  <si>
-    <t>0.8847,0.0735,0.0487,0.0095</t>
-  </si>
-  <si>
-    <t>0.7560,0.3791,0.0055,0.0017</t>
-  </si>
-  <si>
-    <t>0.1243,0.8904,0.0381,0.0022</t>
-  </si>
-  <si>
-    <t>0.0072,0.9171,0.2841,0.0073</t>
-  </si>
-  <si>
-    <t>0.0152,0.0263,0.9666,0.0080</t>
-  </si>
-  <si>
-    <t>0.0379,0.1036,0.9385,0.0063</t>
-  </si>
-  <si>
-    <t>0.0576,0.0221,0.9236,0.0056</t>
-  </si>
-  <si>
-    <t>0.0031,0.3860,0.9658,0.0024</t>
-  </si>
-  <si>
-    <t>0.0059,0.9613,0.0935,0.0021</t>
-  </si>
-  <si>
-    <t>0.0145,0.0229,0.9715,0.0052</t>
-  </si>
-  <si>
-    <t>0.0057,0.9169,0.0054,0.7420</t>
-  </si>
-  <si>
-    <t>0.0122,0.9707,0.0027,0.0146</t>
-  </si>
-  <si>
-    <t>0.0019,0.9875,0.0598,0.0004</t>
-  </si>
-  <si>
-    <t>0.0066,0.9677,0.0435,0.0129</t>
-  </si>
-  <si>
-    <t>0.0316,0.0911,0.9141,0.0269</t>
-  </si>
-  <si>
-    <t>0.0083,0.2052,0.9614,0.0005</t>
-  </si>
-  <si>
-    <t>0.0498,0.0267,0.9157,0.0106</t>
-  </si>
-  <si>
-    <t>0.0369,0.0005,0.9724,0.0015</t>
-  </si>
-  <si>
-    <t>0.0009,0.0061,0.9949,0.0022</t>
-  </si>
-  <si>
-    <t>0.0067,0.0145,0.9836,0.0021</t>
-  </si>
-  <si>
-    <t>0.9665,0.0207,0.0031,0.0040</t>
-  </si>
-  <si>
-    <t>0.9652,0.0219,0.0080,0.0044</t>
-  </si>
-  <si>
-    <t>0.9389,0.0578,0.0106,0.0065</t>
-  </si>
-  <si>
-    <t>0.0069,0.0691,0.9782,0.0056</t>
-  </si>
-  <si>
-    <t>0.9843,0.0027,0.0009,0.0050</t>
-  </si>
-  <si>
-    <t>0.9975,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9568,0.0371,0.0029,0.0028</t>
-  </si>
-  <si>
-    <t>0.0016,0.7776,0.9578,0.0005</t>
-  </si>
-  <si>
-    <t>0.0258,0.1378,0.9572,0.0014</t>
-  </si>
-  <si>
-    <t>0.0042,0.0040,0.9894,0.0041</t>
-  </si>
-  <si>
-    <t>0.0005,0.9352,0.9530,0.0002</t>
-  </si>
-  <si>
-    <t>0.0093,0.0030,0.9849,0.0023</t>
-  </si>
-  <si>
-    <t>0.0172,0.9625,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.0120,0.9774,0.0042,0.0010</t>
-  </si>
-  <si>
-    <t>0.8078,0.0671,0.1996,0.0107</t>
-  </si>
-  <si>
-    <t>0.8311,0.1073,0.0589,0.0031</t>
-  </si>
-  <si>
-    <t>0.0107,0.0718,0.9703,0.0020</t>
-  </si>
-  <si>
-    <t>0.0083,0.5797,0.8741,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.6881,0.9337,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.9789,0.3712,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9353,0.8873,0.0003</t>
-  </si>
-  <si>
-    <t>0.0086,0.0009,0.0409,0.9777</t>
-  </si>
-  <si>
-    <t>0.0017,0.0019,0.0031,0.9972</t>
-  </si>
-  <si>
-    <t>0.0024,0.0095,0.0001,0.9981</t>
-  </si>
-  <si>
-    <t>0.0153,0.0244,0.0054,0.9872</t>
-  </si>
-  <si>
-    <t>0.0094,0.0031,0.0707,0.9721</t>
-  </si>
-  <si>
-    <t>0.0276,0.0041,0.0008,0.9893</t>
-  </si>
-  <si>
-    <t>0.0003,0.9825,0.5787,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.8824,0.9394,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.8086,0.7331,0.0005</t>
-  </si>
-  <si>
-    <t>0.0082,0.2955,0.9506,0.0013</t>
-  </si>
-  <si>
-    <t>0.0017,0.9108,0.6387,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.7402,0.9582,0.0003</t>
-  </si>
-  <si>
-    <t>0.9851,0.0136,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9865,0.0060,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9739,0.0142,0.0020,0.0038</t>
-  </si>
-  <si>
-    <t>0.9880,0.0039,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9800,0.0109,0.0032,0.0020</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0004,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0006,0.0002,0.0026</t>
-  </si>
-  <si>
-    <t>0.9951,0.0003,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.0101,0.0021,0.9888,0.0010</t>
-  </si>
-  <si>
-    <t>0.0269,0.0046,0.9726,0.0013</t>
-  </si>
-  <si>
-    <t>0.6423,0.0120,0.3453,0.0263</t>
-  </si>
-  <si>
-    <t>0.0575,0.0120,0.9478,0.0013</t>
-  </si>
-  <si>
-    <t>0.0910,0.8929,0.0047,0.0114</t>
-  </si>
-  <si>
-    <t>0.0246,0.9638,0.0051,0.0024</t>
-  </si>
-  <si>
-    <t>0.0214,0.9636,0.0033,0.0059</t>
-  </si>
-  <si>
-    <t>0.7089,0.4199,0.0093,0.0020</t>
-  </si>
-  <si>
-    <t>0.0197,0.9688,0.0037,0.0018</t>
-  </si>
-  <si>
-    <t>0.0056,0.9852,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.9400,0.0794,0.0061,0.0010</t>
-  </si>
-  <si>
-    <t>0.7602,0.0457,0.2329,0.0102</t>
-  </si>
-  <si>
-    <t>0.3347,0.0165,0.7305,0.0064</t>
-  </si>
-  <si>
-    <t>0.1322,0.8057,0.0513,0.0863</t>
-  </si>
-  <si>
-    <t>0.6805,0.0501,0.3305,0.0103</t>
-  </si>
-  <si>
-    <t>0.0590,0.2730,0.0699,0.8978</t>
-  </si>
-  <si>
-    <t>0.0098,0.9801,0.0133,0.0023</t>
-  </si>
-  <si>
-    <t>0.0049,0.9837,0.0033,0.0060</t>
-  </si>
-  <si>
-    <t>0.0376,0.9031,0.0380,0.0610</t>
-  </si>
-  <si>
-    <t>0.0061,0.8495,0.7912,0.0021</t>
-  </si>
-  <si>
-    <t>0.0485,0.9533,0.0260,0.0011</t>
-  </si>
-  <si>
-    <t>0.6921,0.3280,0.0538,0.0036</t>
-  </si>
-  <si>
-    <t>0.6405,0.4589,0.0218,0.0034</t>
-  </si>
-  <si>
-    <t>0.9818,0.0096,0.0019,0.0020</t>
-  </si>
-  <si>
-    <t>0.9837,0.0055,0.0018,0.0040</t>
-  </si>
-  <si>
-    <t>0.9894,0.0012,0.0004,0.0044</t>
-  </si>
-  <si>
-    <t>0.9753,0.0098,0.0081,0.0028</t>
-  </si>
-  <si>
-    <t>0.9916,0.0006,0.0002,0.0038</t>
-  </si>
-  <si>
-    <t>0.9606,0.0038,0.0171,0.0085</t>
-  </si>
-  <si>
-    <t>0.9899,0.0010,0.0007,0.0035</t>
-  </si>
-  <si>
-    <t>0.9936,0.0006,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.0177,0.4106,0.8917,0.0018</t>
-  </si>
-  <si>
-    <t>0.0052,0.4885,0.9319,0.0001</t>
-  </si>
-  <si>
-    <t>0.0229,0.0797,0.9470,0.0010</t>
-  </si>
-  <si>
-    <t>0.0235,0.0368,0.9509,0.0013</t>
-  </si>
-  <si>
-    <t>0.6326,0.0642,0.2409,0.0986</t>
-  </si>
-  <si>
-    <t>0.8327,0.0614,0.0347,0.0309</t>
-  </si>
-  <si>
-    <t>0.4572,0.0038,0.7265,0.0032</t>
-  </si>
-  <si>
-    <t>0.8172,0.0153,0.2089,0.0048</t>
-  </si>
-  <si>
-    <t>0.2102,0.0068,0.0029,0.9101</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.0006,0.9989</t>
-  </si>
-  <si>
-    <t>0.0015,0.0065,0.0005,0.9986</t>
-  </si>
-  <si>
-    <t>0.0101,0.0023,0.0363,0.9811</t>
-  </si>
-  <si>
-    <t>0.0048,0.7459,0.8768,0.0019</t>
-  </si>
-  <si>
-    <t>0.9631,0.0154,0.0013,0.0085</t>
-  </si>
-  <si>
-    <t>0.0443,0.9329,0.0025,0.0228</t>
-  </si>
-  <si>
-    <t>0.9842,0.0023,0.0010,0.0063</t>
-  </si>
-  <si>
-    <t>0.8880,0.1019,0.0156,0.0103</t>
-  </si>
-  <si>
-    <t>0.9783,0.0058,0.0022,0.0044</t>
-  </si>
-  <si>
-    <t>0.1993,0.0296,0.0024,0.8713</t>
-  </si>
-  <si>
-    <t>0.9754,0.0023,0.0015,0.0119</t>
-  </si>
-  <si>
-    <t>0.0021,0.1837,0.9758,0.0074</t>
-  </si>
-  <si>
-    <t>0.7767,0.0024,0.0029,0.3266</t>
-  </si>
-  <si>
-    <t>0.9640,0.0054,0.0037,0.0156</t>
-  </si>
-  <si>
-    <t>0.7042,0.3239,0.0091,0.0164</t>
-  </si>
-  <si>
-    <t>0.9514,0.0247,0.0090,0.0020</t>
-  </si>
-  <si>
-    <t>0.9518,0.0387,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.0133,0.9527,0.0091,0.0671</t>
-  </si>
-  <si>
-    <t>0.5714,0.4920,0.0151,0.0219</t>
-  </si>
-  <si>
-    <t>0.8770,0.0942,0.0274,0.0049</t>
-  </si>
-  <si>
-    <t>0.9755,0.0013,0.0005,0.0201</t>
-  </si>
-  <si>
-    <t>0.9876,0.0015,0.0001,0.0047</t>
-  </si>
-  <si>
-    <t>0.9898,0.0025,0.0006,0.0023</t>
-  </si>
-  <si>
-    <t>0.9914,0.0008,0.0002,0.0037</t>
-  </si>
-  <si>
-    <t>0.9904,0.0024,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9793,0.0075,0.0014,0.0042</t>
-  </si>
-  <si>
-    <t>0.9898,0.0017,0.0004,0.0028</t>
-  </si>
-  <si>
-    <t>0.9907,0.0010,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.8290,0.2123,0.0167,0.0072</t>
-  </si>
-  <si>
-    <t>0.9185,0.0819,0.0191,0.0014</t>
-  </si>
-  <si>
-    <t>0.7488,0.3677,0.0093,0.0030</t>
-  </si>
-  <si>
-    <t>0.4566,0.3191,0.3545,0.0121</t>
-  </si>
-  <si>
-    <t>0.9704,0.0125,0.0021,0.0050</t>
-  </si>
-  <si>
-    <t>0.8888,0.0386,0.0549,0.0199</t>
-  </si>
-  <si>
-    <t>0.9078,0.1525,0.0036,0.0015</t>
-  </si>
-  <si>
-    <t>0.7806,0.2015,0.0525,0.0059</t>
-  </si>
-  <si>
-    <t>0.0020,0.0752,0.9902,0.0011</t>
-  </si>
-  <si>
-    <t>0.9453,0.0256,0.0096,0.0089</t>
-  </si>
-  <si>
-    <t>0.0016,0.0029,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0102,0.0123,0.9766,0.0025</t>
-  </si>
-  <si>
-    <t>0.0182,0.0026,0.9833,0.0011</t>
-  </si>
-  <si>
-    <t>0.0465,0.1045,0.8972,0.0019</t>
-  </si>
-  <si>
-    <t>0.0121,0.0024,0.9881,0.0005</t>
-  </si>
-  <si>
-    <t>0.0165,0.0016,0.9856,0.0003</t>
-  </si>
-  <si>
-    <t>0.0148,0.0025,0.9786,0.0030</t>
-  </si>
-  <si>
-    <t>0.3483,0.0348,0.7128,0.0099</t>
-  </si>
-  <si>
-    <t>0.0699,0.0109,0.9454,0.0012</t>
-  </si>
-  <si>
-    <t>0.4981,0.0130,0.6968,0.0017</t>
-  </si>
-  <si>
-    <t>0.2523,0.1202,0.6454,0.0076</t>
-  </si>
-  <si>
-    <t>0.1517,0.0674,0.8105,0.0040</t>
-  </si>
-  <si>
-    <t>0.6434,0.0971,0.2728,0.0048</t>
-  </si>
-  <si>
-    <t>0.6491,0.0906,0.2958,0.0264</t>
-  </si>
-  <si>
-    <t>0.3150,0.0451,0.7459,0.0130</t>
-  </si>
-  <si>
-    <t>0.9444,0.0712,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.5522,0.6183,0.0057,0.0013</t>
-  </si>
-  <si>
-    <t>0.9222,0.1309,0.0042,0.0017</t>
-  </si>
-  <si>
-    <t>0.9849,0.0066,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.9428,0.0367,0.0117,0.0063</t>
-  </si>
-  <si>
-    <t>0.6152,0.0935,0.3288,0.0152</t>
-  </si>
-  <si>
-    <t>0.6171,0.0059,0.3214,0.0537</t>
-  </si>
-  <si>
-    <t>0.7481,0.0173,0.2559,0.0172</t>
-  </si>
-  <si>
-    <t>0.4974,0.0040,0.6678,0.0036</t>
-  </si>
-  <si>
-    <t>0.7299,0.0416,0.2642,0.0243</t>
-  </si>
-  <si>
-    <t>0.0039,0.0086,0.9794,0.0149</t>
-  </si>
-  <si>
-    <t>0.0296,0.1701,0.9187,0.0026</t>
-  </si>
-  <si>
-    <t>0.0259,0.0412,0.9546,0.0012</t>
-  </si>
-  <si>
-    <t>0.0854,0.0059,0.9318,0.0034</t>
-  </si>
-  <si>
-    <t>0.0285,0.1702,0.8973,0.0041</t>
-  </si>
-  <si>
-    <t>0.9933,0.0010,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9932,0.0020,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9922,0.0019,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9878,0.0030,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.9889,0.0040,0.0006,0.0018</t>
-  </si>
-  <si>
-    <t>0.9776,0.0138,0.0019,0.0030</t>
-  </si>
-  <si>
-    <t>0.9963,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9898,0.0010,0.0004,0.0036</t>
-  </si>
-  <si>
-    <t>0.2871,0.0078,0.8095,0.0076</t>
-  </si>
-  <si>
-    <t>0.2766,0.2956,0.4871,0.0112</t>
-  </si>
-  <si>
-    <t>0.8823,0.1046,0.0268,0.0087</t>
-  </si>
-  <si>
-    <t>0.0151,0.0159,0.9789,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0087,0.9952,0.0009</t>
-  </si>
-  <si>
-    <t>0.0491,0.1828,0.7828,0.0082</t>
-  </si>
-  <si>
-    <t>0.0007,0.0059,0.9966,0.0012</t>
-  </si>
-  <si>
-    <t>0.0526,0.0052,0.9461,0.0039</t>
-  </si>
-  <si>
-    <t>0.0093,0.0097,0.9769,0.0106</t>
-  </si>
-  <si>
-    <t>0.0087,0.0127,0.9776,0.0038</t>
-  </si>
-  <si>
-    <t>0.0690,0.0569,0.9044,0.0152</t>
-  </si>
-  <si>
-    <t>0.6523,0.0279,0.3509,0.0276</t>
-  </si>
-  <si>
-    <t>0.7064,0.0077,0.2733,0.0234</t>
-  </si>
-  <si>
-    <t>0.8933,0.0126,0.0641,0.0066</t>
-  </si>
-  <si>
-    <t>0.9922,0.0024,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9967,0.0012,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9939,0.0016,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9849,0.0065,0.0014,0.0018</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9720,0.0155,0.0037,0.0025</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9948,0.0003,0.0001,0.0024</t>
-  </si>
-  <si>
-    <t>0.0395,0.0769,0.8853,0.0123</t>
-  </si>
-  <si>
-    <t>0.0022,0.0544,0.9858,0.0009</t>
-  </si>
-  <si>
-    <t>0.0192,0.0479,0.9501,0.0054</t>
-  </si>
-  <si>
-    <t>0.1122,0.0058,0.9162,0.0011</t>
-  </si>
-  <si>
-    <t>0.0016,0.0055,0.9959,0.0005</t>
-  </si>
-  <si>
-    <t>0.4774,0.0430,0.4698,0.0820</t>
-  </si>
-  <si>
-    <t>0.0801,0.0166,0.8887,0.0416</t>
-  </si>
-  <si>
-    <t>0.0184,0.1149,0.8886,0.0602</t>
-  </si>
-  <si>
-    <t>0.7893,0.0051,0.0051,0.2918</t>
-  </si>
-  <si>
-    <t>0.0559,0.0949,0.0117,0.9536</t>
-  </si>
-  <si>
-    <t>0.0355,0.0075,0.0011,0.9857</t>
-  </si>
-  <si>
-    <t>0.0092,0.0003,0.0003,0.9962</t>
-  </si>
-  <si>
-    <t>0.0021,0.0006,0.0010,0.9980</t>
-  </si>
-  <si>
-    <t>0.8269,0.0327,0.0720,0.0785</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7369,0.0797,0.1969,0.0445</t>
+  </si>
+  <si>
+    <t>0.0133,0.0039,0.0160,0.9833</t>
+  </si>
+  <si>
+    <t>0.7121,0.0176,0.0175,0.3176</t>
+  </si>
+  <si>
+    <t>0.0234,0.0008,0.0005,0.9913</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9916,0.0005,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.9921,0.0015,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.4977,0.0451,0.5895,0.0021</t>
+  </si>
+  <si>
+    <t>0.5689,0.0203,0.5574,0.0059</t>
+  </si>
+  <si>
+    <t>0.6336,0.0130,0.5340,0.0006</t>
+  </si>
+  <si>
+    <t>0.1954,0.0118,0.8519,0.0021</t>
+  </si>
+  <si>
+    <t>0.7755,0.0305,0.2671,0.0064</t>
+  </si>
+  <si>
+    <t>0.0045,0.9885,0.0061,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9958,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.1896,0.8300,0.0058,0.0056</t>
+  </si>
+  <si>
+    <t>0.0600,0.9415,0.0008,0.0033</t>
+  </si>
+  <si>
+    <t>0.0091,0.9829,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.7288,0.0216,0.3037,0.0100</t>
+  </si>
+  <si>
+    <t>0.1637,0.0099,0.8451,0.0133</t>
+  </si>
+  <si>
+    <t>0.0549,0.0103,0.9374,0.0035</t>
+  </si>
+  <si>
+    <t>0.1083,0.0085,0.9194,0.0026</t>
+  </si>
+  <si>
+    <t>0.0257,0.0062,0.9754,0.0007</t>
+  </si>
+  <si>
+    <t>0.0844,0.0024,0.9387,0.0033</t>
+  </si>
+  <si>
+    <t>0.0031,0.0020,0.9923,0.0035</t>
+  </si>
+  <si>
+    <t>0.3157,0.7365,0.0274,0.0076</t>
+  </si>
+  <si>
+    <t>0.8441,0.0678,0.1175,0.0093</t>
+  </si>
+  <si>
+    <t>0.0006,0.0040,0.9945,0.0118</t>
+  </si>
+  <si>
+    <t>0.0042,0.9239,0.2775,0.0001</t>
+  </si>
+  <si>
+    <t>0.8910,0.0560,0.0132,0.0251</t>
+  </si>
+  <si>
+    <t>0.8431,0.1014,0.0616,0.0245</t>
+  </si>
+  <si>
+    <t>0.8551,0.2008,0.0105,0.0020</t>
+  </si>
+  <si>
+    <t>0.0842,0.8912,0.0872,0.0100</t>
+  </si>
+  <si>
+    <t>0.0239,0.6344,0.4114,0.0896</t>
+  </si>
+  <si>
+    <t>0.0756,0.0327,0.9270,0.0026</t>
+  </si>
+  <si>
+    <t>0.0239,0.0356,0.9686,0.0007</t>
+  </si>
+  <si>
+    <t>0.1460,0.0044,0.8699,0.0117</t>
+  </si>
+  <si>
+    <t>0.0337,0.0126,0.9677,0.0004</t>
+  </si>
+  <si>
+    <t>0.0094,0.9363,0.0946,0.0032</t>
+  </si>
+  <si>
+    <t>0.0176,0.0148,0.9620,0.0100</t>
+  </si>
+  <si>
+    <t>0.0118,0.7810,0.0041,0.8595</t>
+  </si>
+  <si>
+    <t>0.0128,0.9650,0.0076,0.0258</t>
+  </si>
+  <si>
+    <t>0.0078,0.9197,0.4882,0.0010</t>
+  </si>
+  <si>
+    <t>0.0021,0.9878,0.0691,0.0008</t>
+  </si>
+  <si>
+    <t>0.0114,0.0647,0.9604,0.0114</t>
+  </si>
+  <si>
+    <t>0.0045,0.1132,0.9836,0.0002</t>
+  </si>
+  <si>
+    <t>0.0398,0.0010,0.9657,0.0015</t>
+  </si>
+  <si>
+    <t>0.0478,0.0015,0.9639,0.0022</t>
+  </si>
+  <si>
+    <t>0.0015,0.0014,0.9962,0.0010</t>
+  </si>
+  <si>
+    <t>0.0024,0.0020,0.9951,0.0007</t>
+  </si>
+  <si>
+    <t>0.9619,0.0322,0.0012,0.0034</t>
+  </si>
+  <si>
+    <t>0.9732,0.0064,0.0031,0.0105</t>
+  </si>
+  <si>
+    <t>0.9824,0.0141,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0110,0.9962,0.0042</t>
+  </si>
+  <si>
+    <t>0.9876,0.0042,0.0013,0.0023</t>
+  </si>
+  <si>
+    <t>0.9906,0.0032,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9885,0.0081,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0048,0.8335,0.7956,0.0043</t>
+  </si>
+  <si>
+    <t>0.0336,0.1118,0.9464,0.0018</t>
+  </si>
+  <si>
+    <t>0.0037,0.0028,0.9918,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.8959,0.9564,0.0001</t>
+  </si>
+  <si>
+    <t>0.0063,0.0143,0.9850,0.0009</t>
+  </si>
+  <si>
+    <t>0.0559,0.8611,0.0533,0.0007</t>
+  </si>
+  <si>
+    <t>0.0080,0.9822,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.8559,0.0729,0.0782,0.0041</t>
+  </si>
+  <si>
+    <t>0.5824,0.0628,0.5032,0.0079</t>
+  </si>
+  <si>
+    <t>0.0073,0.0314,0.9844,0.0035</t>
+  </si>
+  <si>
+    <t>0.0045,0.7174,0.8645,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.2270,0.9593,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9900,0.5002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.8481,0.9077,0.0002</t>
+  </si>
+  <si>
+    <t>0.0095,0.0012,0.0490,0.9775</t>
+  </si>
+  <si>
+    <t>0.0055,0.0007,0.0016,0.9960</t>
+  </si>
+  <si>
+    <t>0.0018,0.1417,0.0004,0.9956</t>
+  </si>
+  <si>
+    <t>0.0145,0.0068,0.0006,0.9921</t>
+  </si>
+  <si>
+    <t>0.0327,0.0134,0.0470,0.9564</t>
+  </si>
+  <si>
+    <t>0.0024,0.0036,0.0013,0.9975</t>
+  </si>
+  <si>
+    <t>0.0003,0.9890,0.4686,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.6949,0.9395,0.0001</t>
+  </si>
+  <si>
+    <t>0.0142,0.6543,0.8231,0.0019</t>
+  </si>
+  <si>
+    <t>0.0175,0.4320,0.8941,0.0023</t>
+  </si>
+  <si>
+    <t>0.0009,0.9855,0.3675,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.7540,0.8313,0.0010</t>
+  </si>
+  <si>
+    <t>0.9933,0.0018,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9825,0.0145,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9843,0.0090,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9925,0.0006,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9935,0.0029,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0021,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9813,0.0138,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0002,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0016,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9950,0.0010,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0040,0.0037,0.9883,0.0053</t>
+  </si>
+  <si>
+    <t>0.0670,0.0030,0.9591,0.0007</t>
+  </si>
+  <si>
+    <t>0.7633,0.0196,0.1872,0.0288</t>
+  </si>
+  <si>
+    <t>0.2015,0.0063,0.8822,0.0013</t>
+  </si>
+  <si>
+    <t>0.0167,0.9730,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.0241,0.9649,0.0035,0.0036</t>
+  </si>
+  <si>
+    <t>0.0943,0.9137,0.0032,0.0037</t>
+  </si>
+  <si>
+    <t>0.8282,0.2562,0.0092,0.0013</t>
+  </si>
+  <si>
+    <t>0.0280,0.9646,0.0018,0.0029</t>
+  </si>
+  <si>
+    <t>0.0043,0.9881,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.4304,0.6751,0.0081,0.0048</t>
+  </si>
+  <si>
+    <t>0.8237,0.0764,0.0715,0.0115</t>
+  </si>
+  <si>
+    <t>0.2763,0.0156,0.7035,0.0462</t>
+  </si>
+  <si>
+    <t>0.8171,0.0131,0.1588,0.0127</t>
+  </si>
+  <si>
+    <t>0.6275,0.0360,0.3520,0.0454</t>
+  </si>
+  <si>
+    <t>0.0871,0.2140,0.0572,0.8995</t>
+  </si>
+  <si>
+    <t>0.0049,0.9893,0.0053,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.9915,0.0078,0.0163</t>
+  </si>
+  <si>
+    <t>0.0618,0.8495,0.0825,0.1380</t>
+  </si>
+  <si>
+    <t>0.0049,0.8771,0.7727,0.0028</t>
+  </si>
+  <si>
+    <t>0.0462,0.9574,0.0266,0.0002</t>
+  </si>
+  <si>
+    <t>0.7668,0.2822,0.0301,0.0015</t>
+  </si>
+  <si>
+    <t>0.8876,0.1712,0.0069,0.0014</t>
+  </si>
+  <si>
+    <t>0.9873,0.0059,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.9907,0.0019,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9911,0.0007,0.0002,0.0044</t>
+  </si>
+  <si>
+    <t>0.9807,0.0039,0.0006,0.0061</t>
+  </si>
+  <si>
+    <t>0.9895,0.0012,0.0007,0.0040</t>
+  </si>
+  <si>
+    <t>0.9415,0.0222,0.0141,0.0157</t>
+  </si>
+  <si>
+    <t>0.9858,0.0010,0.0003,0.0079</t>
+  </si>
+  <si>
+    <t>0.9888,0.0011,0.0006,0.0037</t>
+  </si>
+  <si>
+    <t>0.0178,0.2210,0.9079,0.0037</t>
+  </si>
+  <si>
+    <t>0.0150,0.2541,0.9267,0.0005</t>
+  </si>
+  <si>
+    <t>0.0305,0.5478,0.7912,0.0059</t>
+  </si>
+  <si>
+    <t>0.1444,0.0482,0.8390,0.0039</t>
+  </si>
+  <si>
+    <t>0.7796,0.0109,0.2621,0.0129</t>
+  </si>
+  <si>
+    <t>0.4090,0.0515,0.6366,0.0071</t>
+  </si>
+  <si>
+    <t>0.4619,0.0050,0.6809,0.0084</t>
+  </si>
+  <si>
+    <t>0.6580,0.0450,0.3462,0.0093</t>
+  </si>
+  <si>
+    <t>0.0523,0.0087,0.0014,0.9773</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0014,0.9994</t>
+  </si>
+  <si>
+    <t>0.0007,0.0085,0.0005,0.9989</t>
+  </si>
+  <si>
+    <t>0.0066,0.0032,0.0027,0.9941</t>
+  </si>
+  <si>
+    <t>0.0047,0.9268,0.5089,0.0031</t>
+  </si>
+  <si>
+    <t>0.9781,0.0060,0.0036,0.0059</t>
+  </si>
+  <si>
+    <t>0.3498,0.6811,0.0081,0.0221</t>
+  </si>
+  <si>
+    <t>0.9809,0.0057,0.0005,0.0048</t>
+  </si>
+  <si>
+    <t>0.6787,0.3667,0.0398,0.0085</t>
+  </si>
+  <si>
+    <t>0.8978,0.0264,0.0500,0.0246</t>
+  </si>
+  <si>
+    <t>0.2800,0.0261,0.0094,0.8376</t>
+  </si>
+  <si>
+    <t>0.9730,0.0050,0.0009,0.0090</t>
+  </si>
+  <si>
+    <t>0.0004,0.3770,0.9799,0.0034</t>
+  </si>
+  <si>
+    <t>0.9592,0.0037,0.0051,0.0173</t>
+  </si>
+  <si>
+    <t>0.8476,0.0039,0.0398,0.0745</t>
+  </si>
+  <si>
+    <t>0.4056,0.6569,0.0051,0.0167</t>
+  </si>
+  <si>
+    <t>0.8849,0.0650,0.0099,0.0138</t>
+  </si>
+  <si>
+    <t>0.8149,0.1306,0.0450,0.0079</t>
+  </si>
+  <si>
+    <t>0.0795,0.8849,0.0097,0.0477</t>
+  </si>
+  <si>
+    <t>0.7864,0.1548,0.0766,0.0054</t>
+  </si>
+  <si>
+    <t>0.9221,0.0440,0.0275,0.0038</t>
+  </si>
+  <si>
+    <t>0.9923,0.0007,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9882,0.0028,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.9920,0.0004,0.0001,0.0038</t>
+  </si>
+  <si>
+    <t>0.9940,0.0013,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9834,0.0053,0.0048,0.0021</t>
+  </si>
+  <si>
+    <t>0.9587,0.0159,0.0087,0.0106</t>
+  </si>
+  <si>
+    <t>0.9858,0.0008,0.0004,0.0076</t>
+  </si>
+  <si>
+    <t>0.9809,0.0048,0.0012,0.0057</t>
+  </si>
+  <si>
+    <t>0.8680,0.1871,0.0019,0.0027</t>
+  </si>
+  <si>
+    <t>0.8436,0.2195,0.0095,0.0014</t>
+  </si>
+  <si>
+    <t>0.6814,0.4372,0.0108,0.0028</t>
+  </si>
+  <si>
+    <t>0.0094,0.7242,0.8878,0.0008</t>
+  </si>
+  <si>
+    <t>0.9708,0.0172,0.0031,0.0028</t>
+  </si>
+  <si>
+    <t>0.9526,0.0232,0.0062,0.0079</t>
+  </si>
+  <si>
+    <t>0.9271,0.1165,0.0052,0.0018</t>
+  </si>
+  <si>
+    <t>0.9427,0.0649,0.0100,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0780,0.9950,0.0006</t>
+  </si>
+  <si>
+    <t>0.8244,0.0820,0.1264,0.0035</t>
+  </si>
+  <si>
+    <t>0.0094,0.0025,0.9876,0.0009</t>
+  </si>
+  <si>
+    <t>0.0095,0.0348,0.9786,0.0030</t>
+  </si>
+  <si>
+    <t>0.0190,0.0152,0.9779,0.0004</t>
+  </si>
+  <si>
+    <t>0.0600,0.2211,0.8678,0.0041</t>
+  </si>
+  <si>
+    <t>0.0145,0.0158,0.9768,0.0004</t>
+  </si>
+  <si>
+    <t>0.0106,0.0021,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.0506,0.0218,0.9331,0.0020</t>
+  </si>
+  <si>
+    <t>0.4545,0.0492,0.5632,0.0034</t>
+  </si>
+  <si>
+    <t>0.3944,0.1361,0.4882,0.0111</t>
+  </si>
+  <si>
+    <t>0.6435,0.0195,0.4443,0.0096</t>
+  </si>
+  <si>
+    <t>0.6023,0.0157,0.5488,0.0018</t>
+  </si>
+  <si>
+    <t>0.1485,0.6725,0.1877,0.0029</t>
+  </si>
+  <si>
+    <t>0.7324,0.0224,0.3501,0.0051</t>
+  </si>
+  <si>
+    <t>0.7339,0.0268,0.1897,0.0637</t>
+  </si>
+  <si>
+    <t>0.2212,0.1083,0.6097,0.0019</t>
+  </si>
+  <si>
+    <t>0.8062,0.3533,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.5097,0.6636,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.7222,0.4327,0.0086,0.0010</t>
+  </si>
+  <si>
+    <t>0.9735,0.0240,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9270,0.0678,0.0081,0.0053</t>
+  </si>
+  <si>
+    <t>0.5620,0.1251,0.3578,0.0141</t>
+  </si>
+  <si>
+    <t>0.8578,0.0183,0.1139,0.0102</t>
+  </si>
+  <si>
+    <t>0.7229,0.0442,0.1850,0.0606</t>
+  </si>
+  <si>
+    <t>0.7458,0.0323,0.2497,0.0086</t>
+  </si>
+  <si>
+    <t>0.8003,0.0198,0.1951,0.0219</t>
+  </si>
+  <si>
+    <t>0.0252,0.0114,0.9460,0.0410</t>
+  </si>
+  <si>
+    <t>0.0285,0.1829,0.8992,0.0046</t>
+  </si>
+  <si>
+    <t>0.0386,0.1984,0.9118,0.0034</t>
+  </si>
+  <si>
+    <t>0.1154,0.0047,0.9177,0.0038</t>
+  </si>
+  <si>
+    <t>0.0351,0.0548,0.9133,0.0099</t>
+  </si>
+  <si>
+    <t>0.9880,0.0023,0.0004,0.0031</t>
+  </si>
+  <si>
+    <t>0.9827,0.0120,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.9921,0.0015,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9903,0.0005,0.0002,0.0052</t>
+  </si>
+  <si>
+    <t>0.9853,0.0073,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.9957,0.0006,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0003,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9903,0.0015,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.0448,0.0137,0.9580,0.0012</t>
+  </si>
+  <si>
+    <t>0.5915,0.2256,0.2773,0.0135</t>
+  </si>
+  <si>
+    <t>0.4733,0.0304,0.5131,0.0416</t>
+  </si>
+  <si>
+    <t>0.0205,0.1284,0.9351,0.0004</t>
+  </si>
+  <si>
+    <t>0.0111,0.0240,0.9750,0.0017</t>
+  </si>
+  <si>
+    <t>0.0373,0.0402,0.9215,0.0065</t>
+  </si>
+  <si>
+    <t>0.0008,0.0016,0.9974,0.0008</t>
+  </si>
+  <si>
+    <t>0.0271,0.0438,0.9453,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0679,0.9934,0.0006</t>
+  </si>
+  <si>
+    <t>0.0518,0.0522,0.9080,0.0046</t>
+  </si>
+  <si>
+    <t>0.0635,0.0876,0.8947,0.0217</t>
+  </si>
+  <si>
+    <t>0.6660,0.0083,0.4194,0.0082</t>
+  </si>
+  <si>
+    <t>0.5956,0.0084,0.4468,0.0168</t>
+  </si>
+  <si>
+    <t>0.8403,0.0092,0.1854,0.0058</t>
+  </si>
+  <si>
+    <t>0.9886,0.0036,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9931,0.0018,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0011,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9881,0.0047,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9925,0.0023,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9901,0.0064,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9915,0.0026,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9860,0.0051,0.0015,0.0029</t>
+  </si>
+  <si>
+    <t>0.0140,0.0913,0.9123,0.0022</t>
+  </si>
+  <si>
+    <t>0.0060,0.0347,0.9791,0.0021</t>
+  </si>
+  <si>
+    <t>0.0067,0.0127,0.9771,0.0137</t>
+  </si>
+  <si>
+    <t>0.0212,0.0592,0.9332,0.0026</t>
+  </si>
+  <si>
+    <t>0.0014,0.0028,0.9950,0.0017</t>
+  </si>
+  <si>
+    <t>0.2279,0.0180,0.6459,0.1616</t>
+  </si>
+  <si>
+    <t>0.1628,0.0093,0.8581,0.0177</t>
+  </si>
+  <si>
+    <t>0.0296,0.0079,0.9537,0.0094</t>
+  </si>
+  <si>
+    <t>0.4990,0.0098,0.0264,0.5943</t>
+  </si>
+  <si>
+    <t>0.0019,0.0995,0.0003,0.9958</t>
+  </si>
+  <si>
+    <t>0.0145,0.0041,0.0024,0.9900</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.0043,0.9968</t>
+  </si>
+  <si>
+    <t>0.0040,0.0004,0.0015,0.9968</t>
+  </si>
+  <si>
+    <t>0.7487,0.0120,0.0127,0.2398</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,10 +5059,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
